--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1316-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1316-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1854165-C467-4172-B204-D9480475A6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73DEBF24-F450-4370-AB66-9CE49D0127CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BC2C9944-F8C1-4B6F-83F6-A027BA8CEB1C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{82D2E377-E3F9-4498-8EFE-38177330B6FF}"/>
   </bookViews>
   <sheets>
     <sheet name="1316-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1469,28 +1469,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05847A2-32DB-4A65-BB65-D878AD70F9BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E0041C-A3A4-45A9-A6C0-C37419647E02}">
   <dimension ref="A1:X59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1524,7 +1524,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1680,7 +1680,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2021</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2020</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2019</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2018</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2016</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2015</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2014</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2013</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2012</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2011</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2010</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2009</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2008</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2007</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2006</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2005</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2004</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2003</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2002</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2001</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2000</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>1999</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1998</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>1997</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1996</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>1995</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>1994</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>1993</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>1992</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>1991</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>1990</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="35">
         <v>1989</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="37">
         <v>1988</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
         <v>44</v>
       </c>
